--- a/artfynd/A 7521-2024 artfynd.xlsx
+++ b/artfynd/A 7521-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115229612</v>
+        <v>115228853</v>
       </c>
       <c r="B2" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Barrskog N om Tjurshult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440502</v>
+        <v>440732</v>
       </c>
       <c r="R2" t="n">
-        <v>6391511</v>
+        <v>6391611</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,21 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -810,22 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115229778</v>
+        <v>115229734</v>
       </c>
       <c r="B3" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440471</v>
+        <v>440514</v>
       </c>
       <c r="R3" t="n">
-        <v>6391612</v>
+        <v>6391586</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -927,22 +892,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115229734</v>
+        <v>115229694</v>
       </c>
       <c r="B4" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1009,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1044,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1054,12 +1014,7 @@
         <v>115230060</v>
       </c>
       <c r="B5" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,22 +1116,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115228853</v>
+        <v>115228818</v>
       </c>
       <c r="B6" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440732</v>
+        <v>440762</v>
       </c>
       <c r="R6" t="n">
         <v>6391611</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1278,22 +1228,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115228785</v>
+        <v>115229216</v>
       </c>
       <c r="B7" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,47 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Barrskog N om Tjurshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440762</v>
+        <v>440636</v>
       </c>
       <c r="R7" t="n">
-        <v>6391611</v>
+        <v>6391546</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,21 +1331,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1420,22 +1340,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115229694</v>
+        <v>115229778</v>
       </c>
       <c r="B8" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440514</v>
+        <v>440471</v>
       </c>
       <c r="R8" t="n">
-        <v>6391586</v>
+        <v>6391612</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1502,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1537,7 +1452,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1547,12 +1462,7 @@
         <v>115229519</v>
       </c>
       <c r="B9" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1668,22 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115229216</v>
+        <v>115229594</v>
       </c>
       <c r="B10" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,37 +1596,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Barrskog N om Tjurshult, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440636</v>
+        <v>440502</v>
       </c>
       <c r="R10" t="n">
-        <v>6391546</v>
+        <v>6391511</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1750,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1760,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1785,22 +1704,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115228818</v>
+        <v>115231847</v>
       </c>
       <c r="B11" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,37 +1722,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Barrskog N om Tjurshult, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440762</v>
+        <v>440544</v>
       </c>
       <c r="R11" t="n">
-        <v>6391611</v>
+        <v>6391411</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1867,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1877,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1902,22 +1821,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115229594</v>
+        <v>115228785</v>
       </c>
       <c r="B12" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,36 +1839,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1963,13 +1873,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440502</v>
+        <v>440762</v>
       </c>
       <c r="R12" t="n">
-        <v>6391511</v>
+        <v>6391611</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1998,7 +1908,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2008,7 +1918,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2024,6 +1934,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2033,50 +1958,50 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115231847</v>
+        <v>115229612</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2085,13 +2010,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440544</v>
+        <v>440502</v>
       </c>
       <c r="R13" t="n">
-        <v>6391411</v>
+        <v>6391511</v>
       </c>
       <c r="S13" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2120,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2130,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2146,6 +2071,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2155,7 +2095,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2165,12 +2105,7 @@
         <v>115228902</v>
       </c>
       <c r="B14" t="n">
-        <v>96612</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2287,7 +2222,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus  Hansson , Lars Söderström</t>
+          <t>William Rosén, henrik kullberg, Knut Hasund, Marcus Hansson, Lars Söderström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 7521-2024 artfynd.xlsx
+++ b/artfynd/A 7521-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229694</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115230060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229216</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229778</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229519</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1708,6 +1753,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115231847</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1962,6 +2017,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228785</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2099,6 +2159,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115229612</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2226,8 +2291,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115228902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>